--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N20_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.84553511957509</v>
+        <v>3.874899456930951</v>
       </c>
       <c r="D2" t="n">
-        <v>23.43335696249849</v>
+        <v>3.807920506406005</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
